--- a/machine_learning/zapsync_ai/datasets/file_metadata_v2.xlsx
+++ b/machine_learning/zapsync_ai/datasets/file_metadata_v2.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="46">
   <si>
     <t>Name</t>
   </si>
@@ -98,6 +98,18 @@
     <t>8/2/2025, 11:07:12 PM</t>
   </si>
   <si>
+    <t>1 THE STRATEGIC ROLE OF INFORMATION SYSTEMS (1).pptx</t>
+  </si>
+  <si>
+    <t>PPTX</t>
+  </si>
+  <si>
+    <t>173.67</t>
+  </si>
+  <si>
+    <t>9/8/2025, 11:13:54 AM</t>
+  </si>
+  <si>
     <t>Items Count</t>
   </si>
   <si>
@@ -128,16 +140,16 @@
     <t>8/1/2025, 11:39:43 AM</t>
   </si>
   <si>
-    <t>Software Engineering pdf</t>
-  </si>
-  <si>
-    <t>8/1/2025, 11:40:28 AM</t>
-  </si>
-  <si>
     <t>Machine learning Lessons</t>
   </si>
   <si>
     <t>8/1/2025, 11:40:37 AM</t>
+  </si>
+  <si>
+    <t>Jed's notes</t>
+  </si>
+  <si>
+    <t>9/8/2025, 11:18:58 AM</t>
   </si>
 </sst>
 </file>
@@ -514,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -640,6 +652,23 @@
       </c>
       <c r="E7" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -666,7 +695,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D1" t="s">
         <v>4</v>
@@ -674,86 +703,86 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C2">
         <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C3">
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" t="s">
         <v>34</v>
-      </c>
-      <c r="B4" t="s">
-        <v>30</v>
       </c>
       <c r="C4">
         <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
